--- a/downloads/indicadores/PIB/PIB_datos.xlsx
+++ b/downloads/indicadores/PIB/PIB_datos.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -576,14 +576,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>1T-21</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>44197</v>
+        <v>43101</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>22841359.685</v>
+        <v>23568391.999</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -634,14 +634,14 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2T-21</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>44287</v>
+        <v>43101</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>23949712.898</v>
+        <v>23568391.999</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -692,14 +692,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3T-21</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>44378</v>
+        <v>43101</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>23204796.817</v>
+        <v>23568391.999</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
@@ -750,14 +750,14 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>4T-21</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>44470</v>
+        <v>43101</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>23949712.898</v>
+        <v>23568391.999</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -808,14 +808,14 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>1T-22</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>44562</v>
+        <v>43101</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>23440574.466</v>
+        <v>23568391.999</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -866,14 +866,14 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2T-22</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>44652</v>
+        <v>43101</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>25052395.779</v>
+        <v>23568391.999</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -924,14 +924,14 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3T-22</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>44743</v>
+        <v>43101</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>24289379.479</v>
+        <v>23568391.999</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -982,14 +982,14 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>4T-22</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>44835</v>
+        <v>43101</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>25052395.779</v>
+        <v>23568391.999</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -1040,14 +1040,14 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>1T-23 R</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>44927</v>
+        <v>43101</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>24330982.536</v>
+        <v>23568391.999</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1098,14 +1098,14 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2T-23 R</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>45017</v>
+        <v>43101</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>25590082.607</v>
+        <v>23568391.999</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -1156,14 +1156,14 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3T-23 R</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>45108</v>
+        <v>43101</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>25094793.141</v>
+        <v>23568391.999</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1214,14 +1214,14 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>4T-23 R</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>45200</v>
+        <v>43101</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>25590082.607</v>
+        <v>23568391.999</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -1272,14 +1272,14 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>1T-24 R</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>45292</v>
+        <v>43101</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>24761655.524</v>
+        <v>23568391.999</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1330,14 +1330,14 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2T-24 R</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>45383</v>
+        <v>43101</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>25693292.983</v>
+        <v>24395736.063</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -1388,14 +1388,14 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3T-24 R</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>45474</v>
+        <v>43101</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>25475446.445</v>
+        <v>24137287.71</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1446,15 +1446,13 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>4T-24 R</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>45566</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>25693292.983</v>
-      </c>
+        <v>43101</v>
+      </c>
+      <c r="C21" s="9" t="n"/>
       <c r="D21" s="7" t="inlineStr">
         <is>
           <t>—</t>
@@ -1482,7 +1480,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -1504,15 +1502,13 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>1T-25 R</t>
+          <t>1T-18</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>45658</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>24913610.281</v>
-      </c>
+        <v>43101</v>
+      </c>
+      <c r="C22" s="6" t="n"/>
       <c r="D22" s="4" t="inlineStr">
         <is>
           <t>—</t>
@@ -1540,7 +1536,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1562,14 +1558,14 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2T-25 R</t>
+          <t>2T-18</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>45748</v>
+        <v>43191</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>26135644.696</v>
+        <v>24605265.729</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -1578,12 +1574,12 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -1598,7 +1594,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
@@ -1620,14 +1616,14 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3T-25 R</t>
+          <t>1T-19</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>45839</v>
+        <v>43466</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>25422850.191</v>
+        <v>23790581.652</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
@@ -1636,12 +1632,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1656,7 +1652,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1678,14 +1674,14 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>4T-25 R</t>
+          <t>1T-19</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>45931</v>
+        <v>43466</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>26135644.696</v>
+        <v>23790581.652</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -1694,12 +1690,12 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1714,7 +1710,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Revisado</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -1736,56 +1732,7800 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>24154792.378</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>24024906.35</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>2T-19</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>43556</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>24356643.155</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>19252739.685</v>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>22072209.167</v>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>2T-20</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>43922</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>23504796.547</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>23623455.056</v>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>23204796.817</v>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>2T-21</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>44287</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>23949712.898</v>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>3T-21</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>23204796.817</v>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>4T-21</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>23949712.898</v>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>24310024.252</v>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>24289379.479</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>2T-22</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="n">
+        <v>44652</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>25052395.779</v>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>3T-22</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>24289379.479</v>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>4T-22</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="n">
+        <v>44835</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>25052395.779</v>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>1T-23 R</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I109" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J109" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K109" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C111" s="9" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I111" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C113" s="9" t="n">
+        <v>25108268.25</v>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I113" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J113" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>25094793.141</v>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C115" s="9" t="n"/>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I115" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K115" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>2T-23 R</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="n">
+        <v>45017</v>
+      </c>
+      <c r="C117" s="9" t="n">
+        <v>25590082.607</v>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I117" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K117" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>3T-23 R</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="C118" s="6" t="n">
+        <v>25094793.141</v>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>4T-23 R</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C119" s="9" t="n">
+        <v>25590082.607</v>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I119" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J119" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K119" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>1T-24 R</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C120" s="6" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C121" s="9" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H121" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I121" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J121" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K121" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C122" s="6" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C123" s="9" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H123" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I123" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C124" s="6" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C125" s="9" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H125" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I125" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J125" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K125" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C126" s="6" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C127" s="9" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K127" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C128" s="6" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C129" s="9" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I129" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C130" s="6" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C131" s="9" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C132" s="6" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C133" s="9" t="n">
+        <v>25655479.047</v>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I133" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C134" s="6" t="n">
+        <v>25475446.445</v>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C135" s="9" t="n"/>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I135" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K135" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C136" s="6" t="n"/>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>2T-24 R</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="n">
+        <v>45383</v>
+      </c>
+      <c r="C137" s="9" t="n">
+        <v>25693292.983</v>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I137" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J137" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>3T-24 R</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="C138" s="6" t="n">
+        <v>25475446.445</v>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>4T-24 R</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C139" s="9" t="n">
+        <v>25693292.983</v>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I139" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>1T-25 R</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C140" s="6" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C141" s="9" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I141" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C142" s="6" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C143" s="9" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I143" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K143" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C144" s="6" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C145" s="9" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I145" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J145" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K145" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C146" s="6" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C147" s="9" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H147" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I147" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K147" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C148" s="6" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C149" s="9" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I149" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J149" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K149" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C150" s="6" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C151" s="9" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I151" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J151" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K151" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L151" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C152" s="6" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C153" s="9" t="n">
+        <v>25618678.767</v>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I153" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J153" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K153" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L153" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C154" s="6" t="n">
+        <v>25422850.191</v>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C155" s="9" t="n"/>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I155" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J155" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K155" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L155" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C156" s="6" t="n"/>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>2T-25 R</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C157" s="9" t="n">
+        <v>26135644.696</v>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H157" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I157" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J157" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K157" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L157" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>3T-25 R</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C158" s="6" t="n">
+        <v>25422850.191</v>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>4T-25 R</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C159" s="9" t="n">
+        <v>26135644.696</v>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>+0.9%</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>+1.8%</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I159" s="7" t="inlineStr">
+        <is>
+          <t>Revisado</t>
+        </is>
+      </c>
+      <c r="J159" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K159" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>30 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
           <t>1T-26 P</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B160" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C160" s="6" t="n">
         <v>24973976.071</v>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
         <is>
           <t>-0.6%</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F160" s="4" t="inlineStr">
         <is>
           <t>+0.4%</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Millones de pesos (a precios de 2018)</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
         <is>
           <t>Preliminar</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
         <is>
           <t>30 de julio de 2026</t>
         </is>

--- a/downloads/indicadores/PIB/PIB_datos.xlsx
+++ b/downloads/indicadores/PIB/PIB_datos.xlsx
@@ -507,7 +507,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375 · Fecha de publicación: 30 de julio de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf · Fecha de publicación: 30 de julio de 2026</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">

--- a/downloads/indicadores/PIB/PIB_datos.xlsx
+++ b/downloads/indicadores/PIB/PIB_datos.xlsx
@@ -18,7 +18,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5">
     <font>

--- a/downloads/indicadores/PIB/PIB_datos.xlsx
+++ b/downloads/indicadores/PIB/PIB_datos.xlsx
@@ -2437,7 +2437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2503,14 +2503,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1T-18</t>
+          <t>1T-93</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>43101</v>
+        <v>33970</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>23568391.999</v>
+        <v>13759053.956</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -2536,14 +2536,14 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>1T-18</t>
+          <t>2T-93</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>43101</v>
+        <v>34060</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>24395736.063</v>
+        <v>13889145.022</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -2569,14 +2569,14 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1T-18</t>
+          <t>3T-93</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>43101</v>
+        <v>34151</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>24137287.71</v>
+        <v>13862878.872</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -2602,14 +2602,14 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2T-18</t>
+          <t>4T-93</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>43191</v>
+        <v>34243</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>24605265.729</v>
+        <v>14077352.767</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -2635,14 +2635,14 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1T-19</t>
+          <t>1T-94</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>43466</v>
+        <v>34335</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>23790581.652</v>
+        <v>14100080.574</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -2668,14 +2668,14 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>1T-19</t>
+          <t>2T-94</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>43466</v>
+        <v>34425</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>24154792.378</v>
+        <v>14655082.637</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -2701,14 +2701,14 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>1T-19</t>
+          <t>3T-94</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>43466</v>
+        <v>34516</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>24024906.35</v>
+        <v>14488831.889</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -2734,14 +2734,14 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2T-19</t>
+          <t>4T-94</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>43556</v>
+        <v>34608</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>24356643.155</v>
+        <v>14787062.247</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -2767,14 +2767,14 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>1T-20</t>
+          <t>1T-95</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>43831</v>
+        <v>34700</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>23449993.643</v>
+        <v>14043942.174</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
@@ -2800,14 +2800,14 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>1T-20</t>
+          <t>2T-95</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>43831</v>
+        <v>34790</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>19252739.685</v>
+        <v>13287443.87</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -2833,14 +2833,14 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>1T-20</t>
+          <t>3T-95</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>43831</v>
+        <v>34881</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>22072209.167</v>
+        <v>13412238.39</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
@@ -2866,14 +2866,14 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2T-20</t>
+          <t>4T-95</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>43922</v>
+        <v>34973</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>23504796.547</v>
+        <v>13857623.55</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -2899,14 +2899,14 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>1T-21</t>
+          <t>1T-96</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>44197</v>
+        <v>35065</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>22841359.685</v>
+        <v>14237650.096</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -2932,14 +2932,14 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>1T-21</t>
+          <t>2T-96</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>44197</v>
+        <v>35156</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>23623455.056</v>
+        <v>14340821.386</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -2965,14 +2965,14 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>1T-21</t>
+          <t>3T-96</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>44197</v>
+        <v>35247</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>23204796.817</v>
+        <v>14412887.421</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
@@ -2998,14 +2998,14 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2T-21</t>
+          <t>4T-96</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>44287</v>
+        <v>35339</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>23949712.898</v>
+        <v>15005156.934</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
@@ -3031,14 +3031,14 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>1T-22</t>
+          <t>1T-97</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>44562</v>
+        <v>35431</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>23440574.466</v>
+        <v>14809591.398</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -3064,14 +3064,14 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>1T-22</t>
+          <t>2T-97</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>44562</v>
+        <v>35521</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>24310024.252</v>
+        <v>15584335.623</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
@@ -3097,14 +3097,14 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>1T-22</t>
+          <t>3T-97</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>44562</v>
+        <v>35612</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>24289379.479</v>
+        <v>15624252.001</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
@@ -3130,14 +3130,14 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2T-22</t>
+          <t>4T-97</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>44652</v>
+        <v>35704</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>25052395.779</v>
+        <v>16153434.161</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
@@ -3163,14 +3163,14 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>1T-23</t>
+          <t>1T-98</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>44927</v>
+        <v>35796</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>24330982.536</v>
+        <v>16337214.143</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
@@ -3196,14 +3196,14 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>1T-23</t>
+          <t>2T-98</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>44927</v>
+        <v>35886</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>25108268.25</v>
+        <v>16539597.626</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -3229,14 +3229,14 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>1T-23</t>
+          <t>3T-98</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>44927</v>
+        <v>35977</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>25094793.141</v>
+        <v>16552799.275</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
@@ -3262,14 +3262,14 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2T-23</t>
+          <t>4T-98</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>45017</v>
+        <v>36069</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>25590082.607</v>
+        <v>16587365.488</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
@@ -3295,14 +3295,14 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>1T-24</t>
+          <t>1T-99</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>45292</v>
+        <v>36161</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>24761655.524</v>
+        <v>16704973.282</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
@@ -3328,14 +3328,14 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>1T-24</t>
+          <t>2T-99</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>45292</v>
+        <v>36251</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>25655479.047</v>
+        <v>16929118.024</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -3361,14 +3361,14 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>1T-24</t>
+          <t>3T-99</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>45292</v>
+        <v>36342</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>25475446.445</v>
+        <v>17050482.211</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
@@ -3394,14 +3394,14 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2T-24</t>
+          <t>4T-99</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>45383</v>
+        <v>36434</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>25693292.983</v>
+        <v>17151190.783</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
@@ -3427,14 +3427,14 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>1T-25</t>
+          <t>1T-00</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>45658</v>
+        <v>36526</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>24913610.281</v>
+        <v>17649705.005</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
@@ -3460,14 +3460,14 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>1T-25</t>
+          <t>2T-00</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>45658</v>
+        <v>36617</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>25618678.767</v>
+        <v>17862016.739</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
@@ -3493,14 +3493,14 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>1T-25</t>
+          <t>3T-00</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>45658</v>
+        <v>36708</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>25422850.191</v>
+        <v>18020884.404</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
@@ -3526,14 +3526,14 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2T-25</t>
+          <t>4T-00</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>45748</v>
+        <v>36800</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>26135644.696</v>
+        <v>17714811.387</v>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
@@ -3559,31 +3559,3331 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>1T-01</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>36892</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>17764232.953</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>2T-01</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>36982</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>17874019.34</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>3T-01</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>37073</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>17761059.865</v>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>4T-01</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>37165</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>17526889.778</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>1T-02</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>37257</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>17079137.485</v>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>2T-02</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>37347</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>18016798.15</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>3T-02</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>37438</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>17828003.405</v>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>4T-02</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>37530</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>17834460.01</v>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>1T-03</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>37622</v>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>17609605.878</v>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>2T-03</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>37712</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>18082663.85</v>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>3T-03</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>37803</v>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>17859147.302</v>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>4T-03</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>37895</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>18045854.589</v>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>1T-04</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>37987</v>
+      </c>
+      <c r="C49" s="10" t="n">
+        <v>18185015.464</v>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>2T-04</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>38078</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>18770260.284</v>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>3T-04</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>38169</v>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>18461379.994</v>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>4T-04</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>38261</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>18733374.373</v>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>1T-05</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>38353</v>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>18271688.439</v>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>2T-05</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>38443</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>19218715.204</v>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>3T-05</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>38534</v>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>18883270.709</v>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>4T-05</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>38626</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>19343329.136</v>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>1T-06</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>38718</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>19362570.756</v>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>2T-06</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>38808</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>20116112.951</v>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>3T-06</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>38899</v>
+      </c>
+      <c r="C59" s="10" t="n">
+        <v>19836008.957</v>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>4T-06</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>38991</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>20040523.076</v>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>1T-07</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>39083</v>
+      </c>
+      <c r="C61" s="10" t="n">
+        <v>19745597.365</v>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>2T-07</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>39173</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>20509471.918</v>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3T-07</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>39264</v>
+      </c>
+      <c r="C63" s="10" t="n">
+        <v>20266835.203</v>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>4T-07</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>39356</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>20482204.665</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>1T-08</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>39448</v>
+      </c>
+      <c r="C65" s="10" t="n">
+        <v>19902921.79</v>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>2T-08</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>39539</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>20998503.91</v>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>3T-08</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>39630</v>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>20495872.627</v>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>4T-08</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>39722</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>20370948.404</v>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>1T-09</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>39814</v>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>18537259.148</v>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>2T-09</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>39904</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>18827563.207</v>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>3T-09</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>39995</v>
+      </c>
+      <c r="C71" s="10" t="n">
+        <v>19292209.618</v>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>4T-09</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>40087</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>19963698.743</v>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>1T-10</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>40179</v>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>19371870.871</v>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>2T-10</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>40269</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>20180561.282</v>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>3T-10</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>40360</v>
+      </c>
+      <c r="C75" s="10" t="n">
+        <v>20200797.992</v>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>4T-10</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>40452</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>20676573.452</v>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>1T-11</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>40544</v>
+      </c>
+      <c r="C77" s="10" t="n">
+        <v>20091352.133</v>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>2T-11</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>40634</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>20682934.142</v>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>3T-11</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>40725</v>
+      </c>
+      <c r="C79" s="10" t="n">
+        <v>20950181.653</v>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>4T-11</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>40817</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>21475374.344</v>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>1T-12</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>40909</v>
+      </c>
+      <c r="C81" s="10" t="n">
+        <v>21083780.274</v>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>2T-12</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>21522112.939</v>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>3T-12</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>41091</v>
+      </c>
+      <c r="C83" s="10" t="n">
+        <v>21479008.345</v>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>4T-12</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n">
+        <v>41183</v>
+      </c>
+      <c r="C84" s="11" t="n">
+        <v>22071206.47</v>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>1T-13</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>41275</v>
+      </c>
+      <c r="C85" s="10" t="n">
+        <v>21025801.061</v>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>2T-13</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n">
+        <v>41365</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>21893508.352</v>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>3T-13</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>41456</v>
+      </c>
+      <c r="C87" s="10" t="n">
+        <v>21702816.349</v>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>4T-13</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>41548</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>22268119.789</v>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>1T-14</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>41640</v>
+      </c>
+      <c r="C89" s="10" t="n">
+        <v>21547782.441</v>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>2T-14</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>41730</v>
+      </c>
+      <c r="C90" s="11" t="n">
+        <v>22320155.991</v>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>3T-14</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>41821</v>
+      </c>
+      <c r="C91" s="10" t="n">
+        <v>22258188.342</v>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>4T-14</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="n">
+        <v>41913</v>
+      </c>
+      <c r="C92" s="11" t="n">
+        <v>22939645.045</v>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>1T-15</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>42005</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>22169554.364</v>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>2T-15</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n">
+        <v>42095</v>
+      </c>
+      <c r="C94" s="11" t="n">
+        <v>22843017.522</v>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>3T-15</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>42186</v>
+      </c>
+      <c r="C95" s="10" t="n">
+        <v>23011745.8</v>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>4T-15</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="n">
+        <v>42278</v>
+      </c>
+      <c r="C96" s="11" t="n">
+        <v>23448299.342</v>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>1T-16</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>42370</v>
+      </c>
+      <c r="C97" s="10" t="n">
+        <v>22537031.335</v>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>2T-16</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="n">
+        <v>42461</v>
+      </c>
+      <c r="C98" s="11" t="n">
+        <v>23359955.77</v>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>3T-16</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>42552</v>
+      </c>
+      <c r="C99" s="10" t="n">
+        <v>23214541.358</v>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>4T-16</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="n">
+        <v>42644</v>
+      </c>
+      <c r="C100" s="11" t="n">
+        <v>23982434.514</v>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>1T-17</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>42736</v>
+      </c>
+      <c r="C101" s="10" t="n">
+        <v>23306068.739</v>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>2T-17</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="n">
+        <v>42826</v>
+      </c>
+      <c r="C102" s="11" t="n">
+        <v>23710325.711</v>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>3T-17</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>42917</v>
+      </c>
+      <c r="C103" s="10" t="n">
+        <v>23491266.413</v>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>4T-17</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="n">
+        <v>43009</v>
+      </c>
+      <c r="C104" s="11" t="n">
+        <v>24328768.39</v>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>1T-18</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>43101</v>
+      </c>
+      <c r="C105" s="10" t="n">
+        <v>23568391.999</v>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>2T-18</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="n">
+        <v>43191</v>
+      </c>
+      <c r="C106" s="11" t="n">
+        <v>24395736.063</v>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>3T-18</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>43282</v>
+      </c>
+      <c r="C107" s="10" t="n">
+        <v>24137287.71</v>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>4T-18</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="n">
+        <v>43374</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>24605265.729</v>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C109" s="10" t="n">
+        <v>23790581.652</v>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>2T-19</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="n">
+        <v>43556</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>24154792.378</v>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>3T-19</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>43647</v>
+      </c>
+      <c r="C111" s="10" t="n">
+        <v>24024906.35</v>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>4T-19</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="n">
+        <v>43739</v>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>24356643.155</v>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C113" s="10" t="n">
+        <v>23449993.643</v>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>2T-20</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="n">
+        <v>43922</v>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>19252739.685</v>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>3T-20</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>44013</v>
+      </c>
+      <c r="C115" s="10" t="n">
+        <v>22072209.167</v>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>4T-20</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="n">
+        <v>44105</v>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>23504796.547</v>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C117" s="10" t="n">
+        <v>22841359.685</v>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>2T-21</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="n">
+        <v>44287</v>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>23623455.056</v>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>3T-21</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="C119" s="10" t="n">
+        <v>23204796.817</v>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>4T-21</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>23949712.898</v>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C121" s="10" t="n">
+        <v>23440574.466</v>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>2T-22</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="n">
+        <v>44652</v>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>24310024.252</v>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>3T-22</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="C123" s="10" t="n">
+        <v>24289379.479</v>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>4T-22</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="n">
+        <v>44835</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>25052395.779</v>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C125" s="10" t="n">
+        <v>24330982.536</v>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>2T-23</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="n">
+        <v>45017</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>25108268.25</v>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>3T-23</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="C127" s="10" t="n">
+        <v>25094793.141</v>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>4T-23</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>25590082.607</v>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C129" s="10" t="n">
+        <v>24761655.524</v>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>2T-24</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="n">
+        <v>45383</v>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>25655479.047</v>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>3T-24</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="C131" s="10" t="n">
+        <v>25475446.445</v>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>4T-24</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>25693292.983</v>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C133" s="10" t="n">
+        <v>24913610.281</v>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>2T-25</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C134" s="11" t="n">
+        <v>25618678.767</v>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>3T-25</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C135" s="10" t="n">
+        <v>25422850.191</v>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>4T-25</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C136" s="11" t="n">
+        <v>26135644.696</v>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
           <t>1T-26</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B137" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C137" s="10" t="n">
         <v>24973976.071</v>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Millones de pesos (a precios de 2018)</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
         <is>
           <t>737372</t>
         </is>

--- a/downloads/indicadores/PIB/PIB_datos.xlsx
+++ b/downloads/indicadores/PIB/PIB_datos.xlsx
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Trimestral · Unidad: Porcentaje · Estado: ACTUALIZADO</t>
+          <t>Fuente: INEGI · Frecuencia: Trimestral · Unidad: Porcentaje · Estado: ERROR DE FUENTE</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/PIB/PIB_datos.xlsx
+++ b/downloads/indicadores/PIB/PIB_datos.xlsx
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Trimestral · Unidad: Porcentaje · Estado: ERROR DE FUENTE</t>
+          <t>Fuente: INEGI · Frecuencia: Trimestral · Unidad: Porcentaje · Estado: ACTUALIZADO</t>
         </is>
       </c>
     </row>
